--- a/data/processed/harmonization/Phosphorus__Total_phosphorus/harmonized.xlsx
+++ b/data/processed/harmonization/Phosphorus__Total_phosphorus/harmonized.xlsx
@@ -18874,12 +18874,12 @@
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D358" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E358" s="2" t="inlineStr">
@@ -18909,7 +18909,7 @@
       <c r="K358" s="2" t="inlineStr"/>
       <c r="L358" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18926,12 +18926,12 @@
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D359" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E359" s="2" t="inlineStr">
@@ -18961,7 +18961,7 @@
       <c r="K359" s="2" t="inlineStr"/>
       <c r="L359" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -18978,12 +18978,12 @@
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D360" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E360" s="2" t="inlineStr">
@@ -19013,7 +19013,7 @@
       <c r="K360" s="2" t="inlineStr"/>
       <c r="L360" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19030,12 +19030,12 @@
       </c>
       <c r="C361" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D361" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E361" s="2" t="inlineStr">
@@ -19065,7 +19065,7 @@
       <c r="K361" s="2" t="inlineStr"/>
       <c r="L361" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19082,12 +19082,12 @@
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D362" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E362" s="2" t="inlineStr">
@@ -19117,7 +19117,7 @@
       <c r="K362" s="2" t="inlineStr"/>
       <c r="L362" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19134,12 +19134,12 @@
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D363" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E363" s="2" t="inlineStr">
@@ -19169,7 +19169,7 @@
       <c r="K363" s="2" t="inlineStr"/>
       <c r="L363" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19186,12 +19186,12 @@
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D364" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E364" s="2" t="inlineStr">
@@ -19221,7 +19221,7 @@
       <c r="K364" s="2" t="inlineStr"/>
       <c r="L364" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19238,12 +19238,12 @@
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D365" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E365" s="2" t="inlineStr">
@@ -19273,7 +19273,7 @@
       <c r="K365" s="2" t="inlineStr"/>
       <c r="L365" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19290,12 +19290,12 @@
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D366" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E366" s="2" t="inlineStr">
@@ -19325,7 +19325,7 @@
       <c r="K366" s="2" t="inlineStr"/>
       <c r="L366" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19342,12 +19342,12 @@
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D367" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E367" s="2" t="inlineStr">
@@ -19377,7 +19377,7 @@
       <c r="K367" s="2" t="inlineStr"/>
       <c r="L367" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19394,12 +19394,12 @@
       </c>
       <c r="C368" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D368" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E368" s="2" t="inlineStr">
@@ -19429,7 +19429,7 @@
       <c r="K368" s="2" t="inlineStr"/>
       <c r="L368" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19446,12 +19446,12 @@
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D369" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E369" s="2" t="inlineStr">
@@ -19481,7 +19481,7 @@
       <c r="K369" s="2" t="inlineStr"/>
       <c r="L369" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19498,12 +19498,12 @@
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D370" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E370" s="2" t="inlineStr">
@@ -19533,7 +19533,7 @@
       <c r="K370" s="2" t="inlineStr"/>
       <c r="L370" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19550,12 +19550,12 @@
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D371" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E371" s="2" t="inlineStr">
@@ -19585,7 +19585,7 @@
       <c r="K371" s="2" t="inlineStr"/>
       <c r="L371" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19602,12 +19602,12 @@
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D372" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E372" s="2" t="inlineStr">
@@ -19637,7 +19637,7 @@
       <c r="K372" s="2" t="inlineStr"/>
       <c r="L372" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19654,12 +19654,12 @@
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D373" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E373" s="2" t="inlineStr">
@@ -19689,7 +19689,7 @@
       <c r="K373" s="2" t="inlineStr"/>
       <c r="L373" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19706,12 +19706,12 @@
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D374" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E374" s="2" t="inlineStr">
@@ -19741,7 +19741,7 @@
       <c r="K374" s="2" t="inlineStr"/>
       <c r="L374" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19758,12 +19758,12 @@
       </c>
       <c r="C375" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D375" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E375" s="2" t="inlineStr">
@@ -19793,7 +19793,7 @@
       <c r="K375" s="2" t="inlineStr"/>
       <c r="L375" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19810,12 +19810,12 @@
       </c>
       <c r="C376" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D376" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E376" s="2" t="inlineStr">
@@ -19845,7 +19845,7 @@
       <c r="K376" s="2" t="inlineStr"/>
       <c r="L376" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19862,12 +19862,12 @@
       </c>
       <c r="C377" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D377" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E377" s="2" t="inlineStr">
@@ -19897,7 +19897,7 @@
       <c r="K377" s="2" t="inlineStr"/>
       <c r="L377" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19914,12 +19914,12 @@
       </c>
       <c r="C378" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D378" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E378" s="2" t="inlineStr">
@@ -19949,7 +19949,7 @@
       <c r="K378" s="2" t="inlineStr"/>
       <c r="L378" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -19966,12 +19966,12 @@
       </c>
       <c r="C379" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D379" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E379" s="2" t="inlineStr">
@@ -20001,7 +20001,7 @@
       <c r="K379" s="2" t="inlineStr"/>
       <c r="L379" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20018,12 +20018,12 @@
       </c>
       <c r="C380" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D380" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E380" s="2" t="inlineStr">
@@ -20053,7 +20053,7 @@
       <c r="K380" s="2" t="inlineStr"/>
       <c r="L380" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20070,12 +20070,12 @@
       </c>
       <c r="C381" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D381" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E381" s="2" t="inlineStr">
@@ -20105,7 +20105,7 @@
       <c r="K381" s="2" t="inlineStr"/>
       <c r="L381" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20122,12 +20122,12 @@
       </c>
       <c r="C382" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D382" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E382" s="2" t="inlineStr">
@@ -20157,7 +20157,7 @@
       <c r="K382" s="2" t="inlineStr"/>
       <c r="L382" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20174,12 +20174,12 @@
       </c>
       <c r="C383" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D383" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E383" s="2" t="inlineStr">
@@ -20209,7 +20209,7 @@
       <c r="K383" s="2" t="inlineStr"/>
       <c r="L383" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20226,12 +20226,12 @@
       </c>
       <c r="C384" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D384" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E384" s="2" t="inlineStr">
@@ -20261,7 +20261,7 @@
       <c r="K384" s="2" t="inlineStr"/>
       <c r="L384" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20278,12 +20278,12 @@
       </c>
       <c r="C385" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D385" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E385" s="2" t="inlineStr">
@@ -20313,7 +20313,7 @@
       <c r="K385" s="2" t="inlineStr"/>
       <c r="L385" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20330,12 +20330,12 @@
       </c>
       <c r="C386" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D386" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E386" s="2" t="inlineStr">
@@ -20365,7 +20365,7 @@
       <c r="K386" s="2" t="inlineStr"/>
       <c r="L386" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20382,12 +20382,12 @@
       </c>
       <c r="C387" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D387" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E387" s="2" t="inlineStr">
@@ -20417,7 +20417,7 @@
       <c r="K387" s="2" t="inlineStr"/>
       <c r="L387" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20434,12 +20434,12 @@
       </c>
       <c r="C388" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D388" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E388" s="2" t="inlineStr">
@@ -20469,7 +20469,7 @@
       <c r="K388" s="2" t="inlineStr"/>
       <c r="L388" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20486,12 +20486,12 @@
       </c>
       <c r="C389" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D389" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E389" s="2" t="inlineStr">
@@ -20521,7 +20521,7 @@
       <c r="K389" s="2" t="inlineStr"/>
       <c r="L389" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20538,12 +20538,12 @@
       </c>
       <c r="C390" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D390" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E390" s="2" t="inlineStr">
@@ -20573,7 +20573,7 @@
       <c r="K390" s="2" t="inlineStr"/>
       <c r="L390" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20590,12 +20590,12 @@
       </c>
       <c r="C391" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D391" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E391" s="2" t="inlineStr">
@@ -20625,7 +20625,7 @@
       <c r="K391" s="2" t="inlineStr"/>
       <c r="L391" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20642,12 +20642,12 @@
       </c>
       <c r="C392" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D392" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E392" s="2" t="inlineStr">
@@ -20677,7 +20677,7 @@
       <c r="K392" s="2" t="inlineStr"/>
       <c r="L392" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20694,12 +20694,12 @@
       </c>
       <c r="C393" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D393" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E393" s="2" t="inlineStr">
@@ -20729,7 +20729,7 @@
       <c r="K393" s="2" t="inlineStr"/>
       <c r="L393" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20746,12 +20746,12 @@
       </c>
       <c r="C394" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D394" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E394" s="2" t="inlineStr">
@@ -20781,7 +20781,7 @@
       <c r="K394" s="2" t="inlineStr"/>
       <c r="L394" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20798,12 +20798,12 @@
       </c>
       <c r="C395" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D395" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E395" s="2" t="inlineStr">
@@ -20833,7 +20833,7 @@
       <c r="K395" s="2" t="inlineStr"/>
       <c r="L395" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20850,12 +20850,12 @@
       </c>
       <c r="C396" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D396" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E396" s="2" t="inlineStr">
@@ -20885,7 +20885,7 @@
       <c r="K396" s="2" t="inlineStr"/>
       <c r="L396" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20902,12 +20902,12 @@
       </c>
       <c r="C397" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D397" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E397" s="2" t="inlineStr">
@@ -20937,7 +20937,7 @@
       <c r="K397" s="2" t="inlineStr"/>
       <c r="L397" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -20954,12 +20954,12 @@
       </c>
       <c r="C398" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D398" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E398" s="2" t="inlineStr">
@@ -20989,7 +20989,7 @@
       <c r="K398" s="2" t="inlineStr"/>
       <c r="L398" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21006,12 +21006,12 @@
       </c>
       <c r="C399" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D399" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E399" s="2" t="inlineStr">
@@ -21041,7 +21041,7 @@
       <c r="K399" s="2" t="inlineStr"/>
       <c r="L399" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21058,12 +21058,12 @@
       </c>
       <c r="C400" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D400" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E400" s="2" t="inlineStr">
@@ -21093,7 +21093,7 @@
       <c r="K400" s="2" t="inlineStr"/>
       <c r="L400" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21110,12 +21110,12 @@
       </c>
       <c r="C401" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D401" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E401" s="2" t="inlineStr">
@@ -21145,7 +21145,7 @@
       <c r="K401" s="2" t="inlineStr"/>
       <c r="L401" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21162,12 +21162,12 @@
       </c>
       <c r="C402" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D402" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E402" s="2" t="inlineStr">
@@ -21197,7 +21197,7 @@
       <c r="K402" s="2" t="inlineStr"/>
       <c r="L402" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21214,12 +21214,12 @@
       </c>
       <c r="C403" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D403" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E403" s="2" t="inlineStr">
@@ -21249,7 +21249,7 @@
       <c r="K403" s="2" t="inlineStr"/>
       <c r="L403" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21266,12 +21266,12 @@
       </c>
       <c r="C404" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D404" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E404" s="2" t="inlineStr">
@@ -21301,7 +21301,7 @@
       <c r="K404" s="2" t="inlineStr"/>
       <c r="L404" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21318,12 +21318,12 @@
       </c>
       <c r="C405" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D405" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E405" s="2" t="inlineStr">
@@ -21353,7 +21353,7 @@
       <c r="K405" s="2" t="inlineStr"/>
       <c r="L405" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21370,12 +21370,12 @@
       </c>
       <c r="C406" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D406" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E406" s="2" t="inlineStr">
@@ -21405,7 +21405,7 @@
       <c r="K406" s="2" t="inlineStr"/>
       <c r="L406" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21422,12 +21422,12 @@
       </c>
       <c r="C407" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D407" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E407" s="2" t="inlineStr">
@@ -21457,7 +21457,7 @@
       <c r="K407" s="2" t="inlineStr"/>
       <c r="L407" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21474,12 +21474,12 @@
       </c>
       <c r="C408" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D408" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E408" s="2" t="inlineStr">
@@ -21509,7 +21509,7 @@
       <c r="K408" s="2" t="inlineStr"/>
       <c r="L408" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21526,12 +21526,12 @@
       </c>
       <c r="C409" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D409" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E409" s="2" t="inlineStr">
@@ -21561,7 +21561,7 @@
       <c r="K409" s="2" t="inlineStr"/>
       <c r="L409" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21578,12 +21578,12 @@
       </c>
       <c r="C410" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E410" s="2" t="inlineStr">
@@ -21613,7 +21613,7 @@
       <c r="K410" s="2" t="inlineStr"/>
       <c r="L410" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21630,12 +21630,12 @@
       </c>
       <c r="C411" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E411" s="2" t="inlineStr">
@@ -21665,7 +21665,7 @@
       <c r="K411" s="2" t="inlineStr"/>
       <c r="L411" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21682,12 +21682,12 @@
       </c>
       <c r="C412" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E412" s="2" t="inlineStr">
@@ -21717,7 +21717,7 @@
       <c r="K412" s="2" t="inlineStr"/>
       <c r="L412" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21734,12 +21734,12 @@
       </c>
       <c r="C413" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D413" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E413" s="2" t="inlineStr">
@@ -21769,7 +21769,7 @@
       <c r="K413" s="2" t="inlineStr"/>
       <c r="L413" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21786,12 +21786,12 @@
       </c>
       <c r="C414" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E414" s="2" t="inlineStr">
@@ -21821,7 +21821,7 @@
       <c r="K414" s="2" t="inlineStr"/>
       <c r="L414" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21838,12 +21838,12 @@
       </c>
       <c r="C415" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E415" s="2" t="inlineStr">
@@ -21873,7 +21873,7 @@
       <c r="K415" s="2" t="inlineStr"/>
       <c r="L415" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21890,12 +21890,12 @@
       </c>
       <c r="C416" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D416" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E416" s="2" t="inlineStr">
@@ -21925,7 +21925,7 @@
       <c r="K416" s="2" t="inlineStr"/>
       <c r="L416" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21942,12 +21942,12 @@
       </c>
       <c r="C417" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E417" s="2" t="inlineStr">
@@ -21977,7 +21977,7 @@
       <c r="K417" s="2" t="inlineStr"/>
       <c r="L417" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -21994,12 +21994,12 @@
       </c>
       <c r="C418" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E418" s="2" t="inlineStr">
@@ -22029,7 +22029,7 @@
       <c r="K418" s="2" t="inlineStr"/>
       <c r="L418" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22046,12 +22046,12 @@
       </c>
       <c r="C419" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D419" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E419" s="2" t="inlineStr">
@@ -22081,7 +22081,7 @@
       <c r="K419" s="2" t="inlineStr"/>
       <c r="L419" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22098,12 +22098,12 @@
       </c>
       <c r="C420" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E420" s="2" t="inlineStr">
@@ -22133,7 +22133,7 @@
       <c r="K420" s="2" t="inlineStr"/>
       <c r="L420" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22150,12 +22150,12 @@
       </c>
       <c r="C421" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D421" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E421" s="2" t="inlineStr">
@@ -22185,7 +22185,7 @@
       <c r="K421" s="2" t="inlineStr"/>
       <c r="L421" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22202,12 +22202,12 @@
       </c>
       <c r="C422" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D422" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E422" s="2" t="inlineStr">
@@ -22237,7 +22237,7 @@
       <c r="K422" s="2" t="inlineStr"/>
       <c r="L422" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22254,12 +22254,12 @@
       </c>
       <c r="C423" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D423" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E423" s="2" t="inlineStr">
@@ -22289,7 +22289,7 @@
       <c r="K423" s="2" t="inlineStr"/>
       <c r="L423" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22306,12 +22306,12 @@
       </c>
       <c r="C424" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D424" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E424" s="2" t="inlineStr">
@@ -22341,7 +22341,7 @@
       <c r="K424" s="2" t="inlineStr"/>
       <c r="L424" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22358,12 +22358,12 @@
       </c>
       <c r="C425" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D425" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E425" s="2" t="inlineStr">
@@ -22393,7 +22393,7 @@
       <c r="K425" s="2" t="inlineStr"/>
       <c r="L425" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22410,12 +22410,12 @@
       </c>
       <c r="C426" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E426" s="2" t="inlineStr">
@@ -22445,7 +22445,7 @@
       <c r="K426" s="2" t="inlineStr"/>
       <c r="L426" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22462,12 +22462,12 @@
       </c>
       <c r="C427" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E427" s="2" t="inlineStr">
@@ -22497,7 +22497,7 @@
       <c r="K427" s="2" t="inlineStr"/>
       <c r="L427" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22514,12 +22514,12 @@
       </c>
       <c r="C428" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E428" s="2" t="inlineStr">
@@ -22549,7 +22549,7 @@
       <c r="K428" s="2" t="inlineStr"/>
       <c r="L428" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22566,12 +22566,12 @@
       </c>
       <c r="C429" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E429" s="2" t="inlineStr">
@@ -22601,7 +22601,7 @@
       <c r="K429" s="2" t="inlineStr"/>
       <c r="L429" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22618,12 +22618,12 @@
       </c>
       <c r="C430" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E430" s="2" t="inlineStr">
@@ -22653,7 +22653,7 @@
       <c r="K430" s="2" t="inlineStr"/>
       <c r="L430" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22670,12 +22670,12 @@
       </c>
       <c r="C431" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E431" s="2" t="inlineStr">
@@ -22705,7 +22705,7 @@
       <c r="K431" s="2" t="inlineStr"/>
       <c r="L431" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22722,12 +22722,12 @@
       </c>
       <c r="C432" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D432" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E432" s="2" t="inlineStr">
@@ -22757,7 +22757,7 @@
       <c r="K432" s="2" t="inlineStr"/>
       <c r="L432" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22774,12 +22774,12 @@
       </c>
       <c r="C433" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D433" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E433" s="2" t="inlineStr">
@@ -22809,7 +22809,7 @@
       <c r="K433" s="2" t="inlineStr"/>
       <c r="L433" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22826,12 +22826,12 @@
       </c>
       <c r="C434" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D434" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E434" s="2" t="inlineStr">
@@ -22861,7 +22861,7 @@
       <c r="K434" s="2" t="inlineStr"/>
       <c r="L434" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22878,12 +22878,12 @@
       </c>
       <c r="C435" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E435" s="2" t="inlineStr">
@@ -22913,7 +22913,7 @@
       <c r="K435" s="2" t="inlineStr"/>
       <c r="L435" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22930,12 +22930,12 @@
       </c>
       <c r="C436" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E436" s="2" t="inlineStr">
@@ -22965,7 +22965,7 @@
       <c r="K436" s="2" t="inlineStr"/>
       <c r="L436" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -22982,12 +22982,12 @@
       </c>
       <c r="C437" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D437" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E437" s="2" t="inlineStr">
@@ -23017,7 +23017,7 @@
       <c r="K437" s="2" t="inlineStr"/>
       <c r="L437" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23034,12 +23034,12 @@
       </c>
       <c r="C438" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D438" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E438" s="2" t="inlineStr">
@@ -23069,7 +23069,7 @@
       <c r="K438" s="2" t="inlineStr"/>
       <c r="L438" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23086,12 +23086,12 @@
       </c>
       <c r="C439" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D439" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E439" s="2" t="inlineStr">
@@ -23121,7 +23121,7 @@
       <c r="K439" s="2" t="inlineStr"/>
       <c r="L439" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23138,12 +23138,12 @@
       </c>
       <c r="C440" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E440" s="2" t="inlineStr">
@@ -23173,7 +23173,7 @@
       <c r="K440" s="2" t="inlineStr"/>
       <c r="L440" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23190,12 +23190,12 @@
       </c>
       <c r="C441" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E441" s="2" t="inlineStr">
@@ -23225,7 +23225,7 @@
       <c r="K441" s="2" t="inlineStr"/>
       <c r="L441" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23242,12 +23242,12 @@
       </c>
       <c r="C442" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E442" s="2" t="inlineStr">
@@ -23277,7 +23277,7 @@
       <c r="K442" s="2" t="inlineStr"/>
       <c r="L442" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23294,12 +23294,12 @@
       </c>
       <c r="C443" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D443" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E443" s="2" t="inlineStr">
@@ -23329,7 +23329,7 @@
       <c r="K443" s="2" t="inlineStr"/>
       <c r="L443" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23346,12 +23346,12 @@
       </c>
       <c r="C444" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D444" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E444" s="2" t="inlineStr">
@@ -23381,7 +23381,7 @@
       <c r="K444" s="2" t="inlineStr"/>
       <c r="L444" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23398,12 +23398,12 @@
       </c>
       <c r="C445" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D445" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E445" s="2" t="inlineStr">
@@ -23433,7 +23433,7 @@
       <c r="K445" s="2" t="inlineStr"/>
       <c r="L445" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23450,12 +23450,12 @@
       </c>
       <c r="C446" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D446" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E446" s="2" t="inlineStr">
@@ -23485,7 +23485,7 @@
       <c r="K446" s="2" t="inlineStr"/>
       <c r="L446" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23502,12 +23502,12 @@
       </c>
       <c r="C447" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D447" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E447" s="2" t="inlineStr">
@@ -23537,7 +23537,7 @@
       <c r="K447" s="2" t="inlineStr"/>
       <c r="L447" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23554,12 +23554,12 @@
       </c>
       <c r="C448" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D448" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E448" s="2" t="inlineStr">
@@ -23589,7 +23589,7 @@
       <c r="K448" s="2" t="inlineStr"/>
       <c r="L448" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23606,12 +23606,12 @@
       </c>
       <c r="C449" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D449" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E449" s="2" t="inlineStr">
@@ -23641,7 +23641,7 @@
       <c r="K449" s="2" t="inlineStr"/>
       <c r="L449" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23658,12 +23658,12 @@
       </c>
       <c r="C450" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D450" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E450" s="2" t="inlineStr">
@@ -23693,7 +23693,7 @@
       <c r="K450" s="2" t="inlineStr"/>
       <c r="L450" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23710,12 +23710,12 @@
       </c>
       <c r="C451" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D451" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E451" s="2" t="inlineStr">
@@ -23745,7 +23745,7 @@
       <c r="K451" s="2" t="inlineStr"/>
       <c r="L451" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23762,12 +23762,12 @@
       </c>
       <c r="C452" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D452" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E452" s="2" t="inlineStr">
@@ -23797,7 +23797,7 @@
       <c r="K452" s="2" t="inlineStr"/>
       <c r="L452" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23814,12 +23814,12 @@
       </c>
       <c r="C453" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D453" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E453" s="2" t="inlineStr">
@@ -23849,7 +23849,7 @@
       <c r="K453" s="2" t="inlineStr"/>
       <c r="L453" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23866,12 +23866,12 @@
       </c>
       <c r="C454" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D454" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E454" s="2" t="inlineStr">
@@ -23901,7 +23901,7 @@
       <c r="K454" s="2" t="inlineStr"/>
       <c r="L454" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23918,12 +23918,12 @@
       </c>
       <c r="C455" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D455" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E455" s="2" t="inlineStr">
@@ -23953,7 +23953,7 @@
       <c r="K455" s="2" t="inlineStr"/>
       <c r="L455" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -23970,12 +23970,12 @@
       </c>
       <c r="C456" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D456" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E456" s="2" t="inlineStr">
@@ -24005,7 +24005,7 @@
       <c r="K456" s="2" t="inlineStr"/>
       <c r="L456" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24022,12 +24022,12 @@
       </c>
       <c r="C457" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D457" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E457" s="2" t="inlineStr">
@@ -24057,7 +24057,7 @@
       <c r="K457" s="2" t="inlineStr"/>
       <c r="L457" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24074,12 +24074,12 @@
       </c>
       <c r="C458" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D458" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E458" s="2" t="inlineStr">
@@ -24109,7 +24109,7 @@
       <c r="K458" s="2" t="inlineStr"/>
       <c r="L458" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24126,12 +24126,12 @@
       </c>
       <c r="C459" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D459" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E459" s="2" t="inlineStr">
@@ -24161,7 +24161,7 @@
       <c r="K459" s="2" t="inlineStr"/>
       <c r="L459" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24178,12 +24178,12 @@
       </c>
       <c r="C460" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D460" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E460" s="2" t="inlineStr">
@@ -24213,7 +24213,7 @@
       <c r="K460" s="2" t="inlineStr"/>
       <c r="L460" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24230,12 +24230,12 @@
       </c>
       <c r="C461" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D461" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E461" s="2" t="inlineStr">
@@ -24265,7 +24265,7 @@
       <c r="K461" s="2" t="inlineStr"/>
       <c r="L461" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24282,12 +24282,12 @@
       </c>
       <c r="C462" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D462" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E462" s="2" t="inlineStr">
@@ -24317,7 +24317,7 @@
       <c r="K462" s="2" t="inlineStr"/>
       <c r="L462" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24334,12 +24334,12 @@
       </c>
       <c r="C463" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D463" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E463" s="2" t="inlineStr">
@@ -24369,7 +24369,7 @@
       <c r="K463" s="2" t="inlineStr"/>
       <c r="L463" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24386,12 +24386,12 @@
       </c>
       <c r="C464" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D464" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E464" s="2" t="inlineStr">
@@ -24421,7 +24421,7 @@
       <c r="K464" s="2" t="inlineStr"/>
       <c r="L464" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24438,12 +24438,12 @@
       </c>
       <c r="C465" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D465" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E465" s="2" t="inlineStr">
@@ -24473,7 +24473,7 @@
       <c r="K465" s="2" t="inlineStr"/>
       <c r="L465" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24490,12 +24490,12 @@
       </c>
       <c r="C466" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D466" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E466" s="2" t="inlineStr">
@@ -24525,7 +24525,7 @@
       <c r="K466" s="2" t="inlineStr"/>
       <c r="L466" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24542,12 +24542,12 @@
       </c>
       <c r="C467" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D467" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E467" s="2" t="inlineStr">
@@ -24577,7 +24577,7 @@
       <c r="K467" s="2" t="inlineStr"/>
       <c r="L467" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24594,12 +24594,12 @@
       </c>
       <c r="C468" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D468" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E468" s="2" t="inlineStr">
@@ -24629,7 +24629,7 @@
       <c r="K468" s="2" t="inlineStr"/>
       <c r="L468" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24646,12 +24646,12 @@
       </c>
       <c r="C469" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D469" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E469" s="2" t="inlineStr">
@@ -24681,7 +24681,7 @@
       <c r="K469" s="2" t="inlineStr"/>
       <c r="L469" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24698,12 +24698,12 @@
       </c>
       <c r="C470" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D470" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E470" s="2" t="inlineStr">
@@ -24733,7 +24733,7 @@
       <c r="K470" s="2" t="inlineStr"/>
       <c r="L470" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24750,12 +24750,12 @@
       </c>
       <c r="C471" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D471" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E471" s="2" t="inlineStr">
@@ -24785,7 +24785,7 @@
       <c r="K471" s="2" t="inlineStr"/>
       <c r="L471" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24802,12 +24802,12 @@
       </c>
       <c r="C472" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D472" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E472" s="2" t="inlineStr">
@@ -24837,7 +24837,7 @@
       <c r="K472" s="2" t="inlineStr"/>
       <c r="L472" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24854,12 +24854,12 @@
       </c>
       <c r="C473" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D473" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E473" s="2" t="inlineStr">
@@ -24889,7 +24889,7 @@
       <c r="K473" s="2" t="inlineStr"/>
       <c r="L473" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24906,12 +24906,12 @@
       </c>
       <c r="C474" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D474" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E474" s="2" t="inlineStr">
@@ -24941,7 +24941,7 @@
       <c r="K474" s="2" t="inlineStr"/>
       <c r="L474" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -24958,12 +24958,12 @@
       </c>
       <c r="C475" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D475" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E475" s="2" t="inlineStr">
@@ -24993,7 +24993,7 @@
       <c r="K475" s="2" t="inlineStr"/>
       <c r="L475" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25010,12 +25010,12 @@
       </c>
       <c r="C476" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D476" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E476" s="2" t="inlineStr">
@@ -25045,7 +25045,7 @@
       <c r="K476" s="2" t="inlineStr"/>
       <c r="L476" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25062,12 +25062,12 @@
       </c>
       <c r="C477" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D477" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E477" s="2" t="inlineStr">
@@ -25097,7 +25097,7 @@
       <c r="K477" s="2" t="inlineStr"/>
       <c r="L477" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25114,12 +25114,12 @@
       </c>
       <c r="C478" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D478" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E478" s="2" t="inlineStr">
@@ -25149,7 +25149,7 @@
       <c r="K478" s="2" t="inlineStr"/>
       <c r="L478" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25166,12 +25166,12 @@
       </c>
       <c r="C479" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D479" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E479" s="2" t="inlineStr">
@@ -25201,7 +25201,7 @@
       <c r="K479" s="2" t="inlineStr"/>
       <c r="L479" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25218,12 +25218,12 @@
       </c>
       <c r="C480" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D480" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E480" s="2" t="inlineStr">
@@ -25253,7 +25253,7 @@
       <c r="K480" s="2" t="inlineStr"/>
       <c r="L480" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25270,12 +25270,12 @@
       </c>
       <c r="C481" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D481" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E481" s="2" t="inlineStr">
@@ -25305,7 +25305,7 @@
       <c r="K481" s="2" t="inlineStr"/>
       <c r="L481" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25322,12 +25322,12 @@
       </c>
       <c r="C482" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D482" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E482" s="2" t="inlineStr">
@@ -25357,7 +25357,7 @@
       <c r="K482" s="2" t="inlineStr"/>
       <c r="L482" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25374,12 +25374,12 @@
       </c>
       <c r="C483" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D483" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E483" s="2" t="inlineStr">
@@ -25409,7 +25409,7 @@
       <c r="K483" s="2" t="inlineStr"/>
       <c r="L483" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25426,12 +25426,12 @@
       </c>
       <c r="C484" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D484" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E484" s="2" t="inlineStr">
@@ -25461,7 +25461,7 @@
       <c r="K484" s="2" t="inlineStr"/>
       <c r="L484" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25478,12 +25478,12 @@
       </c>
       <c r="C485" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D485" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E485" s="2" t="inlineStr">
@@ -25513,7 +25513,7 @@
       <c r="K485" s="2" t="inlineStr"/>
       <c r="L485" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25530,12 +25530,12 @@
       </c>
       <c r="C486" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D486" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E486" s="2" t="inlineStr">
@@ -25565,7 +25565,7 @@
       <c r="K486" s="2" t="inlineStr"/>
       <c r="L486" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25582,12 +25582,12 @@
       </c>
       <c r="C487" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D487" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E487" s="2" t="inlineStr">
@@ -25617,7 +25617,7 @@
       <c r="K487" s="2" t="inlineStr"/>
       <c r="L487" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25634,12 +25634,12 @@
       </c>
       <c r="C488" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D488" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E488" s="2" t="inlineStr">
@@ -25669,7 +25669,7 @@
       <c r="K488" s="2" t="inlineStr"/>
       <c r="L488" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25686,12 +25686,12 @@
       </c>
       <c r="C489" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D489" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E489" s="2" t="inlineStr">
@@ -25721,7 +25721,7 @@
       <c r="K489" s="2" t="inlineStr"/>
       <c r="L489" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25738,12 +25738,12 @@
       </c>
       <c r="C490" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D490" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E490" s="2" t="inlineStr">
@@ -25773,7 +25773,7 @@
       <c r="K490" s="2" t="inlineStr"/>
       <c r="L490" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25790,12 +25790,12 @@
       </c>
       <c r="C491" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D491" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E491" s="2" t="inlineStr">
@@ -25825,7 +25825,7 @@
       <c r="K491" s="2" t="inlineStr"/>
       <c r="L491" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25842,12 +25842,12 @@
       </c>
       <c r="C492" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D492" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E492" s="2" t="inlineStr">
@@ -25877,7 +25877,7 @@
       <c r="K492" s="2" t="inlineStr"/>
       <c r="L492" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25894,12 +25894,12 @@
       </c>
       <c r="C493" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D493" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E493" s="2" t="inlineStr">
@@ -25929,7 +25929,7 @@
       <c r="K493" s="2" t="inlineStr"/>
       <c r="L493" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25946,12 +25946,12 @@
       </c>
       <c r="C494" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D494" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E494" s="2" t="inlineStr">
@@ -25981,7 +25981,7 @@
       <c r="K494" s="2" t="inlineStr"/>
       <c r="L494" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -25998,12 +25998,12 @@
       </c>
       <c r="C495" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D495" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E495" s="2" t="inlineStr">
@@ -26033,7 +26033,7 @@
       <c r="K495" s="2" t="inlineStr"/>
       <c r="L495" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26050,12 +26050,12 @@
       </c>
       <c r="C496" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D496" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E496" s="2" t="inlineStr">
@@ -26085,7 +26085,7 @@
       <c r="K496" s="2" t="inlineStr"/>
       <c r="L496" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26102,12 +26102,12 @@
       </c>
       <c r="C497" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D497" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E497" s="2" t="inlineStr">
@@ -26137,7 +26137,7 @@
       <c r="K497" s="2" t="inlineStr"/>
       <c r="L497" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26154,12 +26154,12 @@
       </c>
       <c r="C498" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D498" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E498" s="2" t="inlineStr">
@@ -26189,7 +26189,7 @@
       <c r="K498" s="2" t="inlineStr"/>
       <c r="L498" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26206,12 +26206,12 @@
       </c>
       <c r="C499" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D499" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E499" s="2" t="inlineStr">
@@ -26241,7 +26241,7 @@
       <c r="K499" s="2" t="inlineStr"/>
       <c r="L499" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26258,12 +26258,12 @@
       </c>
       <c r="C500" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D500" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E500" s="2" t="inlineStr">
@@ -26293,7 +26293,7 @@
       <c r="K500" s="2" t="inlineStr"/>
       <c r="L500" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26310,12 +26310,12 @@
       </c>
       <c r="C501" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D501" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E501" s="2" t="inlineStr">
@@ -26345,7 +26345,7 @@
       <c r="K501" s="2" t="inlineStr"/>
       <c r="L501" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26362,12 +26362,12 @@
       </c>
       <c r="C502" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D502" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E502" s="2" t="inlineStr">
@@ -26397,7 +26397,7 @@
       <c r="K502" s="2" t="inlineStr"/>
       <c r="L502" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26414,12 +26414,12 @@
       </c>
       <c r="C503" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D503" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E503" s="2" t="inlineStr">
@@ -26449,7 +26449,7 @@
       <c r="K503" s="2" t="inlineStr"/>
       <c r="L503" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26466,12 +26466,12 @@
       </c>
       <c r="C504" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D504" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E504" s="2" t="inlineStr">
@@ -26501,7 +26501,7 @@
       <c r="K504" s="2" t="inlineStr"/>
       <c r="L504" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26518,12 +26518,12 @@
       </c>
       <c r="C505" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D505" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E505" s="2" t="inlineStr">
@@ -26553,7 +26553,7 @@
       <c r="K505" s="2" t="inlineStr"/>
       <c r="L505" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26570,12 +26570,12 @@
       </c>
       <c r="C506" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D506" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E506" s="2" t="inlineStr">
@@ -26605,7 +26605,7 @@
       <c r="K506" s="2" t="inlineStr"/>
       <c r="L506" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26622,12 +26622,12 @@
       </c>
       <c r="C507" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D507" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E507" s="2" t="inlineStr">
@@ -26657,7 +26657,7 @@
       <c r="K507" s="2" t="inlineStr"/>
       <c r="L507" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26674,12 +26674,12 @@
       </c>
       <c r="C508" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D508" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E508" s="2" t="inlineStr">
@@ -26709,7 +26709,7 @@
       <c r="K508" s="2" t="inlineStr"/>
       <c r="L508" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26726,12 +26726,12 @@
       </c>
       <c r="C509" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D509" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E509" s="2" t="inlineStr">
@@ -26761,7 +26761,7 @@
       <c r="K509" s="2" t="inlineStr"/>
       <c r="L509" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26778,12 +26778,12 @@
       </c>
       <c r="C510" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D510" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E510" s="2" t="inlineStr">
@@ -26813,7 +26813,7 @@
       <c r="K510" s="2" t="inlineStr"/>
       <c r="L510" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26830,12 +26830,12 @@
       </c>
       <c r="C511" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D511" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E511" s="2" t="inlineStr">
@@ -26865,7 +26865,7 @@
       <c r="K511" s="2" t="inlineStr"/>
       <c r="L511" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26882,12 +26882,12 @@
       </c>
       <c r="C512" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D512" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E512" s="2" t="inlineStr">
@@ -26917,7 +26917,7 @@
       <c r="K512" s="2" t="inlineStr"/>
       <c r="L512" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26934,12 +26934,12 @@
       </c>
       <c r="C513" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D513" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E513" s="2" t="inlineStr">
@@ -26969,7 +26969,7 @@
       <c r="K513" s="2" t="inlineStr"/>
       <c r="L513" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -26986,12 +26986,12 @@
       </c>
       <c r="C514" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D514" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E514" s="2" t="inlineStr">
@@ -27021,7 +27021,7 @@
       <c r="K514" s="2" t="inlineStr"/>
       <c r="L514" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27038,12 +27038,12 @@
       </c>
       <c r="C515" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D515" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E515" s="2" t="inlineStr">
@@ -27073,7 +27073,7 @@
       <c r="K515" s="2" t="inlineStr"/>
       <c r="L515" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27090,12 +27090,12 @@
       </c>
       <c r="C516" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D516" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E516" s="2" t="inlineStr">
@@ -27125,7 +27125,7 @@
       <c r="K516" s="2" t="inlineStr"/>
       <c r="L516" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27142,12 +27142,12 @@
       </c>
       <c r="C517" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D517" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E517" s="2" t="inlineStr">
@@ -27177,7 +27177,7 @@
       <c r="K517" s="2" t="inlineStr"/>
       <c r="L517" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27194,12 +27194,12 @@
       </c>
       <c r="C518" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D518" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E518" s="2" t="inlineStr">
@@ -27229,7 +27229,7 @@
       <c r="K518" s="2" t="inlineStr"/>
       <c r="L518" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27246,12 +27246,12 @@
       </c>
       <c r="C519" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D519" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E519" s="2" t="inlineStr">
@@ -27281,7 +27281,7 @@
       <c r="K519" s="2" t="inlineStr"/>
       <c r="L519" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27298,12 +27298,12 @@
       </c>
       <c r="C520" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D520" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E520" s="2" t="inlineStr">
@@ -27333,7 +27333,7 @@
       <c r="K520" s="2" t="inlineStr"/>
       <c r="L520" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27350,12 +27350,12 @@
       </c>
       <c r="C521" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D521" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E521" s="2" t="inlineStr">
@@ -27385,7 +27385,7 @@
       <c r="K521" s="2" t="inlineStr"/>
       <c r="L521" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27402,12 +27402,12 @@
       </c>
       <c r="C522" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D522" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E522" s="2" t="inlineStr">
@@ -27437,7 +27437,7 @@
       <c r="K522" s="2" t="inlineStr"/>
       <c r="L522" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27454,12 +27454,12 @@
       </c>
       <c r="C523" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D523" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E523" s="2" t="inlineStr">
@@ -27489,7 +27489,7 @@
       <c r="K523" s="2" t="inlineStr"/>
       <c r="L523" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27506,12 +27506,12 @@
       </c>
       <c r="C524" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D524" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E524" s="2" t="inlineStr">
@@ -27541,7 +27541,7 @@
       <c r="K524" s="2" t="inlineStr"/>
       <c r="L524" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27558,12 +27558,12 @@
       </c>
       <c r="C525" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D525" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E525" s="2" t="inlineStr">
@@ -27593,7 +27593,7 @@
       <c r="K525" s="2" t="inlineStr"/>
       <c r="L525" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27610,12 +27610,12 @@
       </c>
       <c r="C526" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D526" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E526" s="2" t="inlineStr">
@@ -27645,7 +27645,7 @@
       <c r="K526" s="2" t="inlineStr"/>
       <c r="L526" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27662,12 +27662,12 @@
       </c>
       <c r="C527" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D527" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E527" s="2" t="inlineStr">
@@ -27697,7 +27697,7 @@
       <c r="K527" s="2" t="inlineStr"/>
       <c r="L527" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27714,12 +27714,12 @@
       </c>
       <c r="C528" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D528" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E528" s="2" t="inlineStr">
@@ -27749,7 +27749,7 @@
       <c r="K528" s="2" t="inlineStr"/>
       <c r="L528" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27766,12 +27766,12 @@
       </c>
       <c r="C529" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D529" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E529" s="2" t="inlineStr">
@@ -27801,7 +27801,7 @@
       <c r="K529" s="2" t="inlineStr"/>
       <c r="L529" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27818,12 +27818,12 @@
       </c>
       <c r="C530" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D530" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E530" s="2" t="inlineStr">
@@ -27853,7 +27853,7 @@
       <c r="K530" s="2" t="inlineStr"/>
       <c r="L530" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27870,12 +27870,12 @@
       </c>
       <c r="C531" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D531" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E531" s="2" t="inlineStr">
@@ -27905,7 +27905,7 @@
       <c r="K531" s="2" t="inlineStr"/>
       <c r="L531" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27922,12 +27922,12 @@
       </c>
       <c r="C532" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D532" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E532" s="2" t="inlineStr">
@@ -27957,7 +27957,7 @@
       <c r="K532" s="2" t="inlineStr"/>
       <c r="L532" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -27974,12 +27974,12 @@
       </c>
       <c r="C533" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D533" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E533" s="2" t="inlineStr">
@@ -28009,7 +28009,7 @@
       <c r="K533" s="2" t="inlineStr"/>
       <c r="L533" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28026,12 +28026,12 @@
       </c>
       <c r="C534" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D534" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E534" s="2" t="inlineStr">
@@ -28061,7 +28061,7 @@
       <c r="K534" s="2" t="inlineStr"/>
       <c r="L534" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28078,12 +28078,12 @@
       </c>
       <c r="C535" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D535" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E535" s="2" t="inlineStr">
@@ -28113,7 +28113,7 @@
       <c r="K535" s="2" t="inlineStr"/>
       <c r="L535" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28130,12 +28130,12 @@
       </c>
       <c r="C536" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D536" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E536" s="2" t="inlineStr">
@@ -28165,7 +28165,7 @@
       <c r="K536" s="2" t="inlineStr"/>
       <c r="L536" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28182,12 +28182,12 @@
       </c>
       <c r="C537" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D537" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E537" s="2" t="inlineStr">
@@ -28217,7 +28217,7 @@
       <c r="K537" s="2" t="inlineStr"/>
       <c r="L537" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28234,12 +28234,12 @@
       </c>
       <c r="C538" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D538" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E538" s="2" t="inlineStr">
@@ -28269,7 +28269,7 @@
       <c r="K538" s="2" t="inlineStr"/>
       <c r="L538" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28286,12 +28286,12 @@
       </c>
       <c r="C539" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D539" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E539" s="2" t="inlineStr">
@@ -28321,7 +28321,7 @@
       <c r="K539" s="2" t="inlineStr"/>
       <c r="L539" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28338,12 +28338,12 @@
       </c>
       <c r="C540" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D540" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E540" s="2" t="inlineStr">
@@ -28373,7 +28373,7 @@
       <c r="K540" s="2" t="inlineStr"/>
       <c r="L540" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28390,12 +28390,12 @@
       </c>
       <c r="C541" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D541" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E541" s="2" t="inlineStr">
@@ -28425,7 +28425,7 @@
       <c r="K541" s="2" t="inlineStr"/>
       <c r="L541" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28442,12 +28442,12 @@
       </c>
       <c r="C542" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D542" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E542" s="2" t="inlineStr">
@@ -28477,7 +28477,7 @@
       <c r="K542" s="2" t="inlineStr"/>
       <c r="L542" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28494,12 +28494,12 @@
       </c>
       <c r="C543" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D543" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E543" s="2" t="inlineStr">
@@ -28529,7 +28529,7 @@
       <c r="K543" s="2" t="inlineStr"/>
       <c r="L543" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28546,12 +28546,12 @@
       </c>
       <c r="C544" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D544" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E544" s="2" t="inlineStr">
@@ -28581,7 +28581,7 @@
       <c r="K544" s="2" t="inlineStr"/>
       <c r="L544" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28598,12 +28598,12 @@
       </c>
       <c r="C545" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D545" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E545" s="2" t="inlineStr">
@@ -28633,7 +28633,7 @@
       <c r="K545" s="2" t="inlineStr"/>
       <c r="L545" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28650,12 +28650,12 @@
       </c>
       <c r="C546" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D546" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E546" s="2" t="inlineStr">
@@ -28685,7 +28685,7 @@
       <c r="K546" s="2" t="inlineStr"/>
       <c r="L546" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28702,12 +28702,12 @@
       </c>
       <c r="C547" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D547" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E547" s="2" t="inlineStr">
@@ -28737,7 +28737,7 @@
       <c r="K547" s="2" t="inlineStr"/>
       <c r="L547" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28754,12 +28754,12 @@
       </c>
       <c r="C548" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D548" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E548" s="2" t="inlineStr">
@@ -28789,7 +28789,7 @@
       <c r="K548" s="2" t="inlineStr"/>
       <c r="L548" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28806,12 +28806,12 @@
       </c>
       <c r="C549" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D549" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E549" s="2" t="inlineStr">
@@ -28841,7 +28841,7 @@
       <c r="K549" s="2" t="inlineStr"/>
       <c r="L549" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28858,12 +28858,12 @@
       </c>
       <c r="C550" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D550" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E550" s="2" t="inlineStr">
@@ -28893,7 +28893,7 @@
       <c r="K550" s="2" t="inlineStr"/>
       <c r="L550" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28910,12 +28910,12 @@
       </c>
       <c r="C551" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D551" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E551" s="2" t="inlineStr">
@@ -28945,7 +28945,7 @@
       <c r="K551" s="2" t="inlineStr"/>
       <c r="L551" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -28962,12 +28962,12 @@
       </c>
       <c r="C552" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D552" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E552" s="2" t="inlineStr">
@@ -28997,7 +28997,7 @@
       <c r="K552" s="2" t="inlineStr"/>
       <c r="L552" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29014,12 +29014,12 @@
       </c>
       <c r="C553" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D553" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E553" s="2" t="inlineStr">
@@ -29049,7 +29049,7 @@
       <c r="K553" s="2" t="inlineStr"/>
       <c r="L553" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29066,12 +29066,12 @@
       </c>
       <c r="C554" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D554" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E554" s="2" t="inlineStr">
@@ -29101,7 +29101,7 @@
       <c r="K554" s="2" t="inlineStr"/>
       <c r="L554" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29118,12 +29118,12 @@
       </c>
       <c r="C555" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D555" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E555" s="2" t="inlineStr">
@@ -29153,7 +29153,7 @@
       <c r="K555" s="2" t="inlineStr"/>
       <c r="L555" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29170,12 +29170,12 @@
       </c>
       <c r="C556" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D556" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E556" s="2" t="inlineStr">
@@ -29205,7 +29205,7 @@
       <c r="K556" s="2" t="inlineStr"/>
       <c r="L556" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29222,12 +29222,12 @@
       </c>
       <c r="C557" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D557" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E557" s="2" t="inlineStr">
@@ -29257,7 +29257,7 @@
       <c r="K557" s="2" t="inlineStr"/>
       <c r="L557" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29274,12 +29274,12 @@
       </c>
       <c r="C558" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D558" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E558" s="2" t="inlineStr">
@@ -29309,7 +29309,7 @@
       <c r="K558" s="2" t="inlineStr"/>
       <c r="L558" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29326,12 +29326,12 @@
       </c>
       <c r="C559" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D559" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E559" s="2" t="inlineStr">
@@ -29361,7 +29361,7 @@
       <c r="K559" s="2" t="inlineStr"/>
       <c r="L559" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29378,12 +29378,12 @@
       </c>
       <c r="C560" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D560" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E560" s="2" t="inlineStr">
@@ -29413,7 +29413,7 @@
       <c r="K560" s="2" t="inlineStr"/>
       <c r="L560" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29430,12 +29430,12 @@
       </c>
       <c r="C561" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D561" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E561" s="2" t="inlineStr">
@@ -29465,7 +29465,7 @@
       <c r="K561" s="2" t="inlineStr"/>
       <c r="L561" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29482,12 +29482,12 @@
       </c>
       <c r="C562" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D562" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E562" s="2" t="inlineStr">
@@ -29517,7 +29517,7 @@
       <c r="K562" s="2" t="inlineStr"/>
       <c r="L562" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29534,12 +29534,12 @@
       </c>
       <c r="C563" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D563" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E563" s="2" t="inlineStr">
@@ -29569,7 +29569,7 @@
       <c r="K563" s="2" t="inlineStr"/>
       <c r="L563" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29586,12 +29586,12 @@
       </c>
       <c r="C564" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D564" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E564" s="2" t="inlineStr">
@@ -29621,7 +29621,7 @@
       <c r="K564" s="2" t="inlineStr"/>
       <c r="L564" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29638,12 +29638,12 @@
       </c>
       <c r="C565" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D565" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E565" s="2" t="inlineStr">
@@ -29673,7 +29673,7 @@
       <c r="K565" s="2" t="inlineStr"/>
       <c r="L565" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29690,12 +29690,12 @@
       </c>
       <c r="C566" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D566" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E566" s="2" t="inlineStr">
@@ -29725,7 +29725,7 @@
       <c r="K566" s="2" t="inlineStr"/>
       <c r="L566" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29742,12 +29742,12 @@
       </c>
       <c r="C567" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D567" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E567" s="2" t="inlineStr">
@@ -29777,7 +29777,7 @@
       <c r="K567" s="2" t="inlineStr"/>
       <c r="L567" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29794,12 +29794,12 @@
       </c>
       <c r="C568" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D568" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E568" s="2" t="inlineStr">
@@ -29829,7 +29829,7 @@
       <c r="K568" s="2" t="inlineStr"/>
       <c r="L568" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29846,12 +29846,12 @@
       </c>
       <c r="C569" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D569" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E569" s="2" t="inlineStr">
@@ -29881,7 +29881,7 @@
       <c r="K569" s="2" t="inlineStr"/>
       <c r="L569" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29898,12 +29898,12 @@
       </c>
       <c r="C570" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D570" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E570" s="2" t="inlineStr">
@@ -29933,7 +29933,7 @@
       <c r="K570" s="2" t="inlineStr"/>
       <c r="L570" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -29950,12 +29950,12 @@
       </c>
       <c r="C571" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D571" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E571" s="2" t="inlineStr">
@@ -29985,7 +29985,7 @@
       <c r="K571" s="2" t="inlineStr"/>
       <c r="L571" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30002,12 +30002,12 @@
       </c>
       <c r="C572" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D572" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E572" s="2" t="inlineStr">
@@ -30037,7 +30037,7 @@
       <c r="K572" s="2" t="inlineStr"/>
       <c r="L572" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30054,12 +30054,12 @@
       </c>
       <c r="C573" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D573" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E573" s="2" t="inlineStr">
@@ -30089,7 +30089,7 @@
       <c r="K573" s="2" t="inlineStr"/>
       <c r="L573" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30106,12 +30106,12 @@
       </c>
       <c r="C574" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D574" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E574" s="2" t="inlineStr">
@@ -30141,7 +30141,7 @@
       <c r="K574" s="2" t="inlineStr"/>
       <c r="L574" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30158,12 +30158,12 @@
       </c>
       <c r="C575" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D575" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E575" s="2" t="inlineStr">
@@ -30193,7 +30193,7 @@
       <c r="K575" s="2" t="inlineStr"/>
       <c r="L575" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30210,12 +30210,12 @@
       </c>
       <c r="C576" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D576" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E576" s="2" t="inlineStr">
@@ -30245,7 +30245,7 @@
       <c r="K576" s="2" t="inlineStr"/>
       <c r="L576" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30262,12 +30262,12 @@
       </c>
       <c r="C577" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D577" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E577" s="2" t="inlineStr">
@@ -30297,7 +30297,7 @@
       <c r="K577" s="2" t="inlineStr"/>
       <c r="L577" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30314,12 +30314,12 @@
       </c>
       <c r="C578" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D578" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E578" s="2" t="inlineStr">
@@ -30349,7 +30349,7 @@
       <c r="K578" s="2" t="inlineStr"/>
       <c r="L578" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30366,12 +30366,12 @@
       </c>
       <c r="C579" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D579" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E579" s="2" t="inlineStr">
@@ -30401,7 +30401,7 @@
       <c r="K579" s="2" t="inlineStr"/>
       <c r="L579" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30418,12 +30418,12 @@
       </c>
       <c r="C580" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D580" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E580" s="2" t="inlineStr">
@@ -30453,7 +30453,7 @@
       <c r="K580" s="2" t="inlineStr"/>
       <c r="L580" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30470,12 +30470,12 @@
       </c>
       <c r="C581" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D581" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E581" s="2" t="inlineStr">
@@ -30505,7 +30505,7 @@
       <c r="K581" s="2" t="inlineStr"/>
       <c r="L581" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30522,12 +30522,12 @@
       </c>
       <c r="C582" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D582" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E582" s="2" t="inlineStr">
@@ -30557,7 +30557,7 @@
       <c r="K582" s="2" t="inlineStr"/>
       <c r="L582" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30574,12 +30574,12 @@
       </c>
       <c r="C583" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D583" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E583" s="2" t="inlineStr">
@@ -30609,7 +30609,7 @@
       <c r="K583" s="2" t="inlineStr"/>
       <c r="L583" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30626,12 +30626,12 @@
       </c>
       <c r="C584" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D584" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E584" s="2" t="inlineStr">
@@ -30661,7 +30661,7 @@
       <c r="K584" s="2" t="inlineStr"/>
       <c r="L584" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30678,12 +30678,12 @@
       </c>
       <c r="C585" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D585" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E585" s="2" t="inlineStr">
@@ -30713,7 +30713,7 @@
       <c r="K585" s="2" t="inlineStr"/>
       <c r="L585" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30730,12 +30730,12 @@
       </c>
       <c r="C586" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D586" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E586" s="2" t="inlineStr">
@@ -30765,7 +30765,7 @@
       <c r="K586" s="2" t="inlineStr"/>
       <c r="L586" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30782,12 +30782,12 @@
       </c>
       <c r="C587" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D587" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E587" s="2" t="inlineStr">
@@ -30817,7 +30817,7 @@
       <c r="K587" s="2" t="inlineStr"/>
       <c r="L587" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30834,12 +30834,12 @@
       </c>
       <c r="C588" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D588" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E588" s="2" t="inlineStr">
@@ -30869,7 +30869,7 @@
       <c r="K588" s="2" t="inlineStr"/>
       <c r="L588" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30886,12 +30886,12 @@
       </c>
       <c r="C589" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D589" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E589" s="2" t="inlineStr">
@@ -30921,7 +30921,7 @@
       <c r="K589" s="2" t="inlineStr"/>
       <c r="L589" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30938,12 +30938,12 @@
       </c>
       <c r="C590" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D590" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E590" s="2" t="inlineStr">
@@ -30973,7 +30973,7 @@
       <c r="K590" s="2" t="inlineStr"/>
       <c r="L590" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -30990,12 +30990,12 @@
       </c>
       <c r="C591" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D591" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E591" s="2" t="inlineStr">
@@ -31025,7 +31025,7 @@
       <c r="K591" s="2" t="inlineStr"/>
       <c r="L591" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31042,12 +31042,12 @@
       </c>
       <c r="C592" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D592" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E592" s="2" t="inlineStr">
@@ -31077,7 +31077,7 @@
       <c r="K592" s="2" t="inlineStr"/>
       <c r="L592" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31094,12 +31094,12 @@
       </c>
       <c r="C593" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D593" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E593" s="2" t="inlineStr">
@@ -31129,7 +31129,7 @@
       <c r="K593" s="2" t="inlineStr"/>
       <c r="L593" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31146,12 +31146,12 @@
       </c>
       <c r="C594" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D594" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E594" s="2" t="inlineStr">
@@ -31181,7 +31181,7 @@
       <c r="K594" s="2" t="inlineStr"/>
       <c r="L594" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31198,12 +31198,12 @@
       </c>
       <c r="C595" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D595" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E595" s="2" t="inlineStr">
@@ -31233,7 +31233,7 @@
       <c r="K595" s="2" t="inlineStr"/>
       <c r="L595" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31250,12 +31250,12 @@
       </c>
       <c r="C596" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D596" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E596" s="2" t="inlineStr">
@@ -31285,7 +31285,7 @@
       <c r="K596" s="2" t="inlineStr"/>
       <c r="L596" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31302,12 +31302,12 @@
       </c>
       <c r="C597" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D597" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E597" s="2" t="inlineStr">
@@ -31337,7 +31337,7 @@
       <c r="K597" s="2" t="inlineStr"/>
       <c r="L597" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31354,12 +31354,12 @@
       </c>
       <c r="C598" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D598" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E598" s="2" t="inlineStr">
@@ -31389,7 +31389,7 @@
       <c r="K598" s="2" t="inlineStr"/>
       <c r="L598" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31406,12 +31406,12 @@
       </c>
       <c r="C599" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D599" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E599" s="2" t="inlineStr">
@@ -31441,7 +31441,7 @@
       <c r="K599" s="2" t="inlineStr"/>
       <c r="L599" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31458,12 +31458,12 @@
       </c>
       <c r="C600" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D600" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E600" s="2" t="inlineStr">
@@ -31493,7 +31493,7 @@
       <c r="K600" s="2" t="inlineStr"/>
       <c r="L600" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31510,12 +31510,12 @@
       </c>
       <c r="C601" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D601" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E601" s="2" t="inlineStr">
@@ -31545,7 +31545,7 @@
       <c r="K601" s="2" t="inlineStr"/>
       <c r="L601" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31562,12 +31562,12 @@
       </c>
       <c r="C602" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D602" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E602" s="2" t="inlineStr">
@@ -31597,7 +31597,7 @@
       <c r="K602" s="2" t="inlineStr"/>
       <c r="L602" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31614,12 +31614,12 @@
       </c>
       <c r="C603" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D603" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E603" s="2" t="inlineStr">
@@ -31649,7 +31649,7 @@
       <c r="K603" s="2" t="inlineStr"/>
       <c r="L603" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31666,12 +31666,12 @@
       </c>
       <c r="C604" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D604" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E604" s="2" t="inlineStr">
@@ -31701,7 +31701,7 @@
       <c r="K604" s="2" t="inlineStr"/>
       <c r="L604" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31718,12 +31718,12 @@
       </c>
       <c r="C605" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D605" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E605" s="2" t="inlineStr">
@@ -31753,7 +31753,7 @@
       <c r="K605" s="2" t="inlineStr"/>
       <c r="L605" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31770,12 +31770,12 @@
       </c>
       <c r="C606" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D606" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E606" s="2" t="inlineStr">
@@ -31805,7 +31805,7 @@
       <c r="K606" s="2" t="inlineStr"/>
       <c r="L606" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31822,12 +31822,12 @@
       </c>
       <c r="C607" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D607" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E607" s="2" t="inlineStr">
@@ -31857,7 +31857,7 @@
       <c r="K607" s="2" t="inlineStr"/>
       <c r="L607" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31874,12 +31874,12 @@
       </c>
       <c r="C608" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D608" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E608" s="2" t="inlineStr">
@@ -31909,7 +31909,7 @@
       <c r="K608" s="2" t="inlineStr"/>
       <c r="L608" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31926,12 +31926,12 @@
       </c>
       <c r="C609" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D609" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E609" s="2" t="inlineStr">
@@ -31961,7 +31961,7 @@
       <c r="K609" s="2" t="inlineStr"/>
       <c r="L609" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -31978,12 +31978,12 @@
       </c>
       <c r="C610" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D610" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E610" s="2" t="inlineStr">
@@ -32013,7 +32013,7 @@
       <c r="K610" s="2" t="inlineStr"/>
       <c r="L610" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32030,12 +32030,12 @@
       </c>
       <c r="C611" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D611" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E611" s="2" t="inlineStr">
@@ -32065,7 +32065,7 @@
       <c r="K611" s="2" t="inlineStr"/>
       <c r="L611" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32082,12 +32082,12 @@
       </c>
       <c r="C612" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D612" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E612" s="2" t="inlineStr">
@@ -32117,7 +32117,7 @@
       <c r="K612" s="2" t="inlineStr"/>
       <c r="L612" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32134,12 +32134,12 @@
       </c>
       <c r="C613" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D613" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E613" s="2" t="inlineStr">
@@ -32169,7 +32169,7 @@
       <c r="K613" s="2" t="inlineStr"/>
       <c r="L613" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32186,12 +32186,12 @@
       </c>
       <c r="C614" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D614" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E614" s="2" t="inlineStr">
@@ -32221,7 +32221,7 @@
       <c r="K614" s="2" t="inlineStr"/>
       <c r="L614" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32238,12 +32238,12 @@
       </c>
       <c r="C615" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D615" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E615" s="2" t="inlineStr">
@@ -32273,7 +32273,7 @@
       <c r="K615" s="2" t="inlineStr"/>
       <c r="L615" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32290,12 +32290,12 @@
       </c>
       <c r="C616" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D616" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E616" s="2" t="inlineStr">
@@ -32325,7 +32325,7 @@
       <c r="K616" s="2" t="inlineStr"/>
       <c r="L616" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32342,12 +32342,12 @@
       </c>
       <c r="C617" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D617" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E617" s="2" t="inlineStr">
@@ -32377,7 +32377,7 @@
       <c r="K617" s="2" t="inlineStr"/>
       <c r="L617" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32394,12 +32394,12 @@
       </c>
       <c r="C618" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D618" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E618" s="2" t="inlineStr">
@@ -32429,7 +32429,7 @@
       <c r="K618" s="2" t="inlineStr"/>
       <c r="L618" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32446,12 +32446,12 @@
       </c>
       <c r="C619" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D619" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E619" s="2" t="inlineStr">
@@ -32481,7 +32481,7 @@
       <c r="K619" s="2" t="inlineStr"/>
       <c r="L619" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32498,12 +32498,12 @@
       </c>
       <c r="C620" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D620" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E620" s="2" t="inlineStr">
@@ -32533,7 +32533,7 @@
       <c r="K620" s="2" t="inlineStr"/>
       <c r="L620" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32550,12 +32550,12 @@
       </c>
       <c r="C621" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D621" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E621" s="2" t="inlineStr">
@@ -32585,7 +32585,7 @@
       <c r="K621" s="2" t="inlineStr"/>
       <c r="L621" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32602,12 +32602,12 @@
       </c>
       <c r="C622" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D622" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E622" s="2" t="inlineStr">
@@ -32637,7 +32637,7 @@
       <c r="K622" s="2" t="inlineStr"/>
       <c r="L622" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32654,12 +32654,12 @@
       </c>
       <c r="C623" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D623" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E623" s="2" t="inlineStr">
@@ -32689,7 +32689,7 @@
       <c r="K623" s="2" t="inlineStr"/>
       <c r="L623" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32706,12 +32706,12 @@
       </c>
       <c r="C624" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D624" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E624" s="2" t="inlineStr">
@@ -32741,7 +32741,7 @@
       <c r="K624" s="2" t="inlineStr"/>
       <c r="L624" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32758,12 +32758,12 @@
       </c>
       <c r="C625" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D625" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E625" s="2" t="inlineStr">
@@ -32793,7 +32793,7 @@
       <c r="K625" s="2" t="inlineStr"/>
       <c r="L625" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32810,12 +32810,12 @@
       </c>
       <c r="C626" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D626" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E626" s="2" t="inlineStr">
@@ -32845,7 +32845,7 @@
       <c r="K626" s="2" t="inlineStr"/>
       <c r="L626" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32862,12 +32862,12 @@
       </c>
       <c r="C627" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D627" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E627" s="2" t="inlineStr">
@@ -32897,7 +32897,7 @@
       <c r="K627" s="2" t="inlineStr"/>
       <c r="L627" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32914,12 +32914,12 @@
       </c>
       <c r="C628" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D628" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E628" s="2" t="inlineStr">
@@ -32949,7 +32949,7 @@
       <c r="K628" s="2" t="inlineStr"/>
       <c r="L628" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -32966,12 +32966,12 @@
       </c>
       <c r="C629" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D629" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E629" s="2" t="inlineStr">
@@ -33001,7 +33001,7 @@
       <c r="K629" s="2" t="inlineStr"/>
       <c r="L629" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33018,12 +33018,12 @@
       </c>
       <c r="C630" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D630" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E630" s="2" t="inlineStr">
@@ -33053,7 +33053,7 @@
       <c r="K630" s="2" t="inlineStr"/>
       <c r="L630" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33070,12 +33070,12 @@
       </c>
       <c r="C631" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D631" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E631" s="2" t="inlineStr">
@@ -33105,7 +33105,7 @@
       <c r="K631" s="2" t="inlineStr"/>
       <c r="L631" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33122,12 +33122,12 @@
       </c>
       <c r="C632" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D632" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E632" s="2" t="inlineStr">
@@ -33157,7 +33157,7 @@
       <c r="K632" s="2" t="inlineStr"/>
       <c r="L632" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33174,12 +33174,12 @@
       </c>
       <c r="C633" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D633" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E633" s="2" t="inlineStr">
@@ -33209,7 +33209,7 @@
       <c r="K633" s="2" t="inlineStr"/>
       <c r="L633" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33226,12 +33226,12 @@
       </c>
       <c r="C634" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D634" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E634" s="2" t="inlineStr">
@@ -33261,7 +33261,7 @@
       <c r="K634" s="2" t="inlineStr"/>
       <c r="L634" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33278,12 +33278,12 @@
       </c>
       <c r="C635" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D635" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E635" s="2" t="inlineStr">
@@ -33313,7 +33313,7 @@
       <c r="K635" s="2" t="inlineStr"/>
       <c r="L635" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33330,12 +33330,12 @@
       </c>
       <c r="C636" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D636" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E636" s="2" t="inlineStr">
@@ -33365,7 +33365,7 @@
       <c r="K636" s="2" t="inlineStr"/>
       <c r="L636" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33382,12 +33382,12 @@
       </c>
       <c r="C637" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D637" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E637" s="2" t="inlineStr">
@@ -33417,7 +33417,7 @@
       <c r="K637" s="2" t="inlineStr"/>
       <c r="L637" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33434,12 +33434,12 @@
       </c>
       <c r="C638" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D638" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E638" s="2" t="inlineStr">
@@ -33469,7 +33469,7 @@
       <c r="K638" s="2" t="inlineStr"/>
       <c r="L638" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33486,12 +33486,12 @@
       </c>
       <c r="C639" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D639" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E639" s="2" t="inlineStr">
@@ -33521,7 +33521,7 @@
       <c r="K639" s="2" t="inlineStr"/>
       <c r="L639" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33538,12 +33538,12 @@
       </c>
       <c r="C640" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D640" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E640" s="2" t="inlineStr">
@@ -33573,7 +33573,7 @@
       <c r="K640" s="2" t="inlineStr"/>
       <c r="L640" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33590,12 +33590,12 @@
       </c>
       <c r="C641" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D641" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E641" s="2" t="inlineStr">
@@ -33625,7 +33625,7 @@
       <c r="K641" s="2" t="inlineStr"/>
       <c r="L641" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33642,12 +33642,12 @@
       </c>
       <c r="C642" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D642" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E642" s="2" t="inlineStr">
@@ -33677,7 +33677,7 @@
       <c r="K642" s="2" t="inlineStr"/>
       <c r="L642" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33694,12 +33694,12 @@
       </c>
       <c r="C643" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D643" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E643" s="2" t="inlineStr">
@@ -33729,7 +33729,7 @@
       <c r="K643" s="2" t="inlineStr"/>
       <c r="L643" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33746,12 +33746,12 @@
       </c>
       <c r="C644" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D644" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E644" s="2" t="inlineStr">
@@ -33781,7 +33781,7 @@
       <c r="K644" s="2" t="inlineStr"/>
       <c r="L644" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33798,12 +33798,12 @@
       </c>
       <c r="C645" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D645" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E645" s="2" t="inlineStr">
@@ -33833,7 +33833,7 @@
       <c r="K645" s="2" t="inlineStr"/>
       <c r="L645" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33850,12 +33850,12 @@
       </c>
       <c r="C646" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D646" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E646" s="2" t="inlineStr">
@@ -33885,7 +33885,7 @@
       <c r="K646" s="2" t="inlineStr"/>
       <c r="L646" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33902,12 +33902,12 @@
       </c>
       <c r="C647" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D647" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E647" s="2" t="inlineStr">
@@ -33937,7 +33937,7 @@
       <c r="K647" s="2" t="inlineStr"/>
       <c r="L647" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -33954,12 +33954,12 @@
       </c>
       <c r="C648" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D648" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E648" s="2" t="inlineStr">
@@ -33989,7 +33989,7 @@
       <c r="K648" s="2" t="inlineStr"/>
       <c r="L648" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -34006,12 +34006,12 @@
       </c>
       <c r="C649" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D649" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E649" s="2" t="inlineStr">
@@ -34041,7 +34041,7 @@
       <c r="K649" s="2" t="inlineStr"/>
       <c r="L649" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -34058,12 +34058,12 @@
       </c>
       <c r="C650" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D650" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E650" s="2" t="inlineStr">
@@ -34093,7 +34093,7 @@
       <c r="K650" s="2" t="inlineStr"/>
       <c r="L650" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -34110,12 +34110,12 @@
       </c>
       <c r="C651" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D651" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E651" s="2" t="inlineStr">
@@ -34145,7 +34145,7 @@
       <c r="K651" s="2" t="inlineStr"/>
       <c r="L651" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -34162,12 +34162,12 @@
       </c>
       <c r="C652" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D652" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E652" s="2" t="inlineStr">
@@ -34197,7 +34197,7 @@
       <c r="K652" s="2" t="inlineStr"/>
       <c r="L652" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column P (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
